--- a/request_forms/013_fashion_retail_display_mannequins_requisition_form--request_forms.xlsx
+++ b/request_forms/013_fashion_retail_display_mannequins_requisition_form--request_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="41" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -525,13 +525,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>store_name</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>Store Name</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Enter the name of the store</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -548,13 +552,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>department</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>Department</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Select the department</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -571,13 +579,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>category</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Select the category</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -594,13 +606,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>request_date</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>Request Date</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Enter the request date</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -617,13 +633,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>delivery_date</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>Delivery Date</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Enter the delivery date</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -640,13 +660,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>delivery_time</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>Delivery Time</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Enter the delivery time</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -663,13 +687,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>quantity</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>Quantity</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Enter the quantity</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -686,13 +714,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>contact_name</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>Contact Name</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Enter the contact name</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -709,13 +741,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>phone_number</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>Phone Number</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Enter the phone number</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -732,13 +768,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>email_address</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>Email Address</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Enter the email address</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -755,13 +795,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>store_number</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>Store Number</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Select the store number</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -778,36 +822,44 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>location</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>Location</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Select the location</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>remarks</t>
+          <t>approval_status</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>remarks</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>Approval Status</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Select the approval status</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -819,18 +871,22 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>approval_status</t>
+          <t>approval_by</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>approval_status</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>Approval By</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Select the approval by</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -842,61 +898,73 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>approval_by</t>
+          <t>delivery_confirmation</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>approval_by</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
+          <t>Delivery Confirmation</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Select the delivery confirmation</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>approval_date</t>
+          <t>delivery_notes</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>approval_date</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
+          <t>Delivery Notes</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Enter the delivery notes</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>delivery_confirmation</t>
+          <t>remarks</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>delivery_confirmation</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
+          <t>Remarks</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Enter any remarks</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
           <t>no</t>
@@ -906,20 +974,24 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>delivery_confirmation_by</t>
+          <t>approval_date</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>delivery_confirmation_by</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
+          <t>Approval Date</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Enter the approval date</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
           <t>no</t>
@@ -939,10 +1011,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>delivery_confirmation_date</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
+          <t>Delivery Confirmation Date</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Enter the delivery confirmation date</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
           <t>no</t>
@@ -952,20 +1028,24 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>delivery_notes</t>
+          <t>delivery_confirmation_by</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>delivery_notes</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
+          <t>Delivery Confirmation By</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Select the delivery confirmation by</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
           <t>no</t>
@@ -975,113 +1055,25 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>remarks</t>
+          <t>delivery_confirmation_status</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>remarks</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
+          <t>Delivery Confirmation Status</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Select the delivery confirmation status</t>
+        </is>
+      </c>
       <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>store_name</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>store_name</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>department</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>department</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>category</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>category</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>quantity</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>quantity</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,12 +1090,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1123,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'men'}</t>
+          <t>men</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'Men'}</t>
+          <t>Men</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1140,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'women'}</t>
+          <t>women</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Women'}</t>
+          <t>Women</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1157,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'tops'}</t>
+          <t>tops</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Tops'}</t>
+          <t>Tops</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1174,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'bottoms'}</t>
+          <t>bottoms</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Bottoms'}</t>
+          <t>Bottoms</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1191,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'dresses'}</t>
+          <t>dresses</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Dresses'}</t>
+          <t>Dresses</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1208,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'store_1'}</t>
+          <t>store_1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Store 1'}</t>
+          <t>Store 1</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1225,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'store_2'}</t>
+          <t>store_2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Store 2'}</t>
+          <t>Store 2</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1242,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'location_1'}</t>
+          <t>location_1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Location 1'}</t>
+          <t>Location 1</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1259,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'location_2'}</t>
+          <t>location_2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'Location 2'}</t>
+          <t>Location 2</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1276,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'pending'}</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'Pending'}</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1293,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'approved'}</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'Approved'}</t>
+          <t>Approved</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1310,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'rejected'}</t>
+          <t>rejected</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'Rejected'}</t>
+          <t>Rejected</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1327,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'john'}</t>
+          <t>john</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'John'}</t>
+          <t>John</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1344,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'jane'}</t>
+          <t>jane</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'Jane'}</t>
+          <t>Jane</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1361,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'confirmed'}</t>
+          <t>confirmed</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 'Confirmed'}</t>
+          <t>Confirmed</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1378,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_'not_confirmed'}</t>
+          <t>not_confirmed</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 'Not Confirmed'}</t>
+          <t>Not Confirmed</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1395,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_'john'}</t>
+          <t>john</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': 'John'}</t>
+          <t>John</t>
         </is>
       </c>
     </row>
@@ -1420,97 +1412,46 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'value':_'jane'}</t>
+          <t>jane</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'value': 'Jane'}</t>
+          <t>Jane</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>department_choices</t>
+          <t>delivery_confirmation_status_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'value':_'men'}</t>
+          <t>confirmed</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'value': 'Men'}</t>
+          <t>Confirmed</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>department_choices</t>
+          <t>delivery_confirmation_status_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'value':_'women'}</t>
+          <t>not_confirmed</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'value': 'Women'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>category_choices</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>{'value':_'tops'}</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>{'value': 'Tops'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>category_choices</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>{'value':_'bottoms'}</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>{'value': 'Bottoms'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>category_choices</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>{'value':_'dresses'}</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>{'value': 'Dresses'}</t>
+          <t>Not Confirmed</t>
         </is>
       </c>
     </row>
